--- a/Tables/WEAPON_DATA.xlsx
+++ b/Tables/WEAPON_DATA.xlsx
@@ -848,32 +848,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Label</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">RobotID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AmmoKind</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필드</t>
+          <t xml:space="preserve">한글 라벨</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">수치</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">한글 라벨</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">수치</t>
         </is>
@@ -882,105 +882,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RobotID</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t xml:space="preserve">로봇A</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">관통</t>
+        </is>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RobotID</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t xml:space="preserve">로봇B</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표준</t>
+        </is>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AmmoKind</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관통</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폭발</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AmmoKind</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">표준</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>2</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누적형 드론</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AmmoKind</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">폭발</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AmmoKind</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">누적형 드론</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AmmoKind</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">광역형 드론</t>
         </is>
       </c>
-      <c r="C9">
+      <c r="E7">
         <v>5</v>
       </c>
     </row>
@@ -994,133 +955,69 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">WEAPON_DATA 테이블 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">INDEX</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FieldName</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DataType</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번호</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">필드명</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">간략 설명</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 타입</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 예시</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">필드 설명/값</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고(근거)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dev_Index</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발용 번호</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
+          <t xml:space="preserve">필드 설명 / 값</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dev_Desc</t>
+          <t xml:space="preserve">Dev_Index</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">개발용 설명</t>
+          <t xml:space="preserve">개발용 번호</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로봇A 관통탄</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,60 +1026,62 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">행을 한눈에</t>
+          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Dev_Desc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유 번호</t>
+          <t xml:space="preserve">개발용 설명</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>1</v>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로봇A 관통탄</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1부터</t>
+          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">행 식별</t>
+          <t xml:space="preserve">행을 한눈에</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RobotID</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇</t>
+          <t xml:space="preserve">고유 번호</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">enum</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E6">
@@ -1190,27 +1089,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇A1 로봇B2</t>
+          <t xml:space="preserve">1부터</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Designer_Data 참조</t>
+          <t xml:space="preserve">행 식별</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmmoKind</t>
+          <t xml:space="preserve">RobotID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">탄종</t>
+          <t xml:space="preserve">로봇</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1223,7 +1122,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">관통1 표준2 폭발3 누적형4 광역형5</t>
+          <t xml:space="preserve">로봇A1 로봇B2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1234,82 +1133,82 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damage</t>
+          <t xml:space="preserve">AmmoKind</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">발당 피해</t>
+          <t xml:space="preserve">탄종</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">enum</t>
         </is>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 발이 주는 피해</t>
+          <t xml:space="preserve">관통1 표준2 폭발3 누적형4 광역형5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">json params dA0/dA1/dA2 (✅ confirmed)</t>
+          <t xml:space="preserve">Designer_Data 참조</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShotsPerSec</t>
+          <t xml:space="preserve">Damage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">초당 발사</t>
+          <t xml:space="preserve">발당 피해</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 줄이 1초에 쏘는 수</t>
+          <t xml:space="preserve">한 발이 주는 피해</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">json params pA0/pA1/pA2 (✅ confirmed) · ⚠️ **LineSpec 과 어느 쪽이 정본인지 설계 미결**(§73-28)</t>
+          <t xml:space="preserve">json params dA0/dA1/dA2 (✅ confirmed)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LineSpec</t>
+          <t xml:space="preserve">ShotsPerSec</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">라인 스펙</t>
+          <t xml:space="preserve">초당 발사</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1318,163 +1217,163 @@
         </is>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">줄 하나의 명목 발사율</t>
+          <t xml:space="preserve">그 줄이 1초에 쏘는 수</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">json params specA0/specA1/specA2 (✅ confirmed) · ⚠️ **ShotsPerSec 과 정본 미결**(§73-28)</t>
+          <t xml:space="preserve">json params pA0/pA1/pA2 (✅ confirmed) · ⚠️ **LineSpec 과 어느 쪽이 정본인지 설계 미결**(§73-28)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShotsPerRound</t>
+          <t xml:space="preserve">LineSpec</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 발당 나가는 수</t>
+          <t xml:space="preserve">라인 스펙</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">float</t>
         </is>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">탄 한 발을 소비할 때 나가는 발</t>
+          <t xml:space="preserve">줄 하나의 명목 발사율</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.shotsPerRound · ✅ **사용자 확정 09-18**(세 발) · 1 이면 구 거동</t>
+          <t xml:space="preserve">json params specA0/specA1/specA2 (✅ confirmed) · ⚠️ **ShotsPerSec 과 정본 미결**(§73-28)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShotDamageFactor</t>
+          <t xml:space="preserve">ShotsPerRound</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 발 피해 배수</t>
+          <t xml:space="preserve">한 발당 나가는 수</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">쪼갠 한 발의 피해 배수</t>
+          <t xml:space="preserve">탄 한 발을 소비할 때 나가는 발</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.shotDamageFactor · ✅ **사용자 확정 09-18**(1/2) · ⚠️ 총량은 3 x 1/2 = **1.5배** — 「1초 피해 = 명목 출력」 계약이 그만큼 바뀐다</t>
+          <t xml:space="preserve">CombatTuning.shotsPerRound · ✅ **사용자 확정 09-18**(세 발) · 1 이면 구 거동</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge</t>
+          <t xml:space="preserve">ShotDamageFactor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">충전량</t>
+          <t xml:space="preserve">한 발 피해 배수</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">float</t>
         </is>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">드론 한 기가 가진 피해 총량</t>
+          <t xml:space="preserve">쪼갠 한 발의 피해 배수</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">json params dB (✅ confirmed) · 로봇A 행은 0(해당 없음)</t>
+          <t xml:space="preserve">CombatTuning.shotDamageFactor · ✅ **사용자 확정 09-18**(1/2) · ⚠️ 총량은 3 x 1/2 = **1.5배** — 「1초 피해 = 명목 출력」 계약이 그만큼 바뀐다</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoeDamageFactor</t>
+          <t xml:space="preserve">Charge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역 피해 배수</t>
+          <t xml:space="preserve">충전량</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">표적 하나에 주는 피해의 비</t>
+          <t xml:space="preserve">드론 한 기가 가진 피해 총량</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">누적형 1.0 · 광역형 = json params droneAoeDamageFactor (⚠️ confirmed false) · 무기 스펙트럼 좌표 dBAoe 50 으로 이관은 W02 문안 뒤</t>
+          <t xml:space="preserve">json params dB (✅ confirmed) · 로봇A 행은 0(해당 없음)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HitInterval</t>
+          <t xml:space="preserve">AoeDamageFactor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">타격 간격</t>
+          <t xml:space="preserve">광역 피해 배수</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1483,31 +1382,31 @@
         </is>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">붙어서 몇 초마다 때리는가</t>
+          <t xml:space="preserve">표적 하나에 주는 피해의 비</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.droneHitIntervalTbd · ⚠️ 가정</t>
+          <t xml:space="preserve">누적형 1.0 · 광역형 = json params droneAoeDamageFactor (⚠️ confirmed false) · 무기 스펙트럼 좌표 dBAoe 50 으로 이관은 W02 문안 뒤</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DamageFraction</t>
+          <t xml:space="preserve">HitInterval</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">기당 피해 몫</t>
+          <t xml:space="preserve">타격 간격</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1516,47 +1415,80 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 번에 쓰는 충전량의 비</t>
+          <t xml:space="preserve">붙어서 몇 초마다 때리는가</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.droneDamageFractionTbd · ⚠️ 가정(열 번에 나눠 쓴다)</t>
+          <t xml:space="preserve">CombatTuning.droneHitIntervalTbd · ⚠️ 가정</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageFraction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기당 피해 몫</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 번에 쓰는 충전량의 비</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CombatTuning.droneDamageFractionTbd · ⚠️ 가정(열 번에 나눠 쓴다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">bool</t>
         </is>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">1=확정 0=가정</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">**행마다 원천의 confirmed 를 그대로** — 로봇A 셋과 누적형은 1, 광역형은 droneAoeDamageFactor 가 미확정이라 0</t>
         </is>

--- a/Tables/WEAPON_DATA.xlsx
+++ b/Tables/WEAPON_DATA.xlsx
@@ -397,7 +397,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L7">
         <v>0.5</v>
@@ -409,7 +409,7 @@
         <v>0.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L7">
         <v>0.5</v>
@@ -835,7 +835,7 @@
         <v>0.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">충전량</t>
+          <t xml:space="preserve">충전량(기당 피해 좌표)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">json params dB (✅ confirmed) · 로봇A 행은 0(해당 없음)</t>
+          <t xml:space="preserve">✅ **무기 스펙트럼 좌표** — 누적형 dB 100 · 광역형 dBAoe **50**(2026-09-19 이관 · `260918_W02` 5장). ⚠️ **이 칸이 광역형의 대가를 든다** — AoeDamageFactor 는 여기서 나눠 나오는 파생값이다. 로봇A 행은 0(해당 없음)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">누적형 1.0 · 광역형 = json params droneAoeDamageFactor (⚠️ confirmed false) · 무기 스펙트럼 좌표 dBAoe 50 으로 이관은 W02 문안 뒤</t>
+          <t xml:space="preserve">🗑️ **읽는 곳이 없다 — 파생값이다**(2026-09-19 이관 완료). 생성기는 Charge 둘을 나눠 배수를 낸다(50 ÷ 100 = 0.5). 열을 남긴 까닭은 사람이 **좌표와 몫을 견줄 수 있어야** 하기 때문이다 — 여기 수를 고쳐도 게임은 안 바뀐다. 고칠 곳은 Charge 다</t>
         </is>
       </c>
     </row>

--- a/Tables/WEAPON_DATA.xlsx
+++ b/Tables/WEAPON_DATA.xlsx
@@ -66,25 +66,30 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t xml:space="preserve">DamagePerUnit</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Charge</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">AoeDamageFactor</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">HitInterval</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">DamageFraction</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
@@ -143,25 +148,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve">기당 피해 좌표</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">충전량</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">광역 피해 배수</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">타격 간격</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">기당 피해 몫</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
@@ -213,6 +223,9 @@
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>1</v>
       </c>
     </row>
@@ -262,6 +275,9 @@
         <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>1</v>
       </c>
     </row>
@@ -311,6 +327,9 @@
         <v>0</v>
       </c>
       <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>1</v>
       </c>
     </row>
@@ -351,15 +370,18 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
         <v>0.5</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.1</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>1</v>
       </c>
     </row>
@@ -400,15 +422,18 @@
         <v>50</v>
       </c>
       <c r="L7">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>0.5</v>
       </c>
       <c r="N7">
+        <v>0.5</v>
+      </c>
+      <c r="O7">
         <v>0.1</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1</v>
       </c>
     </row>
@@ -472,25 +497,30 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t xml:space="preserve">DamagePerUnit</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Charge</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">AoeDamageFactor</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">HitInterval</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">DamageFraction</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
@@ -549,25 +579,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve">기당 피해 좌표</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">충전량</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">광역 피해 배수</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">타격 간격</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">기당 피해 몫</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
@@ -623,6 +658,9 @@
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>1</v>
       </c>
     </row>
@@ -676,6 +714,9 @@
         <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>1</v>
       </c>
     </row>
@@ -729,6 +770,9 @@
         <v>0</v>
       </c>
       <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>1</v>
       </c>
     </row>
@@ -773,15 +817,18 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
         <v>0.5</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.1</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>1</v>
       </c>
     </row>
@@ -826,15 +873,18 @@
         <v>50</v>
       </c>
       <c r="L7">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>0.5</v>
       </c>
       <c r="N7">
+        <v>0.5</v>
+      </c>
+      <c r="O7">
         <v>0.1</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1</v>
       </c>
     </row>
@@ -1335,12 +1385,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charge</t>
+          <t xml:space="preserve">DamagePerUnit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">충전량(기당 피해 좌표)</t>
+          <t xml:space="preserve">기당 피해 좌표</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1353,7 +1403,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">드론 한 기가 가진 피해 총량</t>
+          <t xml:space="preserve">드론 한 기가 한 번에 주는 피해</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1368,30 +1418,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoeDamageFactor</t>
+          <t xml:space="preserve">Charge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역 피해 배수</t>
+          <t xml:space="preserve">충전량</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">표적 하나에 주는 피해의 비</t>
+          <t xml:space="preserve">드론 한 기가 가진 피해 총량(= 수명)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ **읽는 곳이 없다 — 파생값이다**(2026-09-19 이관 완료). 생성기는 Charge 둘을 나눠 배수를 낸다(50 ÷ 100 = 0.5). 열을 남긴 까닭은 사람이 **좌표와 몫을 견줄 수 있어야** 하기 때문이다 — 여기 수를 고쳐도 게임은 안 바뀐다. 고칠 곳은 Charge 다</t>
+          <t xml:space="preserve">json params dB (✅ confirmed) — **두 종이 같은 100 이다.** ⚠️⚠️ **기당 피해와 다른 축이다**(`260918_W02` 3장). 광역형의 기당 피해가 절반이라고 **충전량까지 절반이 아니다** — 09-18 에 그 둘을 한 수로 두어 **광역형 수명이 두 배가 된** 결함이 있었다. 로봇A 행은 0(해당 없음)</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1451,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HitInterval</t>
+          <t xml:space="preserve">AoeDamageFactor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">타격 간격</t>
+          <t xml:space="preserve">광역 피해 배수</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1415,16 +1465,16 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">붙어서 몇 초마다 때리는가</t>
+          <t xml:space="preserve">표적 하나에 주는 피해의 비</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.droneHitIntervalTbd · ⚠️ 가정</t>
+          <t xml:space="preserve">🗑️ **읽는 곳이 없다 — 파생값이다**(2026-09-19 이관 완료). 생성기는 Charge 둘을 나눠 배수를 낸다(50 ÷ 100 = 0.5). 열을 남긴 까닭은 사람이 **좌표와 몫을 견줄 수 있어야** 하기 때문이다 — 여기 수를 고쳐도 게임은 안 바뀐다. 고칠 곳은 Charge 다</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1484,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DamageFraction</t>
+          <t xml:space="preserve">HitInterval</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">기당 피해 몫</t>
+          <t xml:space="preserve">타격 간격</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1448,16 +1498,16 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 번에 쓰는 충전량의 비</t>
+          <t xml:space="preserve">붙어서 몇 초마다 때리는가</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CombatTuning.droneDamageFractionTbd · ⚠️ 가정(열 번에 나눠 쓴다)</t>
+          <t xml:space="preserve">CombatTuning.droneHitIntervalTbd · ⚠️ 가정</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1517,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t xml:space="preserve">DamageFraction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기당 피해 몫</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>0.1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 번에 쓰는 충전량의 비</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CombatTuning.droneDamageFractionTbd · ⚠️ 가정(열 번에 나눠 쓴다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">bool</t>
         </is>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">1=확정 0=가정</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">**행마다 원천의 confirmed 를 그대로** — 로봇A 셋과 누적형은 1, 광역형은 droneAoeDamageFactor 가 미확정이라 0</t>
         </is>

--- a/Tables/WEAPON_DATA.xlsx
+++ b/Tables/WEAPON_DATA.xlsx
@@ -158,7 +158,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역 피해 배수</t>
+          <t xml:space="preserve">광역 피해 배수(파생·안 읽음)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역 피해 배수</t>
+          <t xml:space="preserve">광역 피해 배수(파생·안 읽음)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
